--- a/Fantasy unificado/roster.xlsx
+++ b/Fantasy unificado/roster.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Evolucoes/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3CA14E4-2249-4B98-A3E0-47247A6C8E58}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8CEADB7-D625-4CA9-8123-BD4FA2F3FDF8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="698">
   <si>
     <t>team_id</t>
   </si>
@@ -1684,48 +1684,6 @@
   </si>
   <si>
     <t>nome_time_2</t>
-  </si>
-  <si>
-    <t>J1R1S2526</t>
-  </si>
-  <si>
-    <t>J2R1S2526</t>
-  </si>
-  <si>
-    <t>J3R1S2526</t>
-  </si>
-  <si>
-    <t>J4R1S2526</t>
-  </si>
-  <si>
-    <t>J5R1S2526</t>
-  </si>
-  <si>
-    <t>J6R1S2526</t>
-  </si>
-  <si>
-    <t>J7R1S2526</t>
-  </si>
-  <si>
-    <t>J1R2S2526</t>
-  </si>
-  <si>
-    <t>J2R2S2526</t>
-  </si>
-  <si>
-    <t>J3R2S2526</t>
-  </si>
-  <si>
-    <t>J4R2S2526</t>
-  </si>
-  <si>
-    <t>J5R2S2526</t>
-  </si>
-  <si>
-    <t>J6R2S2526</t>
-  </si>
-  <si>
-    <t>J7R2S2526</t>
   </si>
   <si>
     <t>transactiondate</t>
@@ -17949,24 +17907,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>605</v>
+        <v>591</v>
       </c>
       <c r="B1" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="C1" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="D1" t="s">
-        <v>608</v>
+        <v>594</v>
       </c>
       <c r="E1" t="s">
-        <v>609</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="B2">
         <v>7</v>
@@ -17983,7 +17941,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>610</v>
+        <v>596</v>
       </c>
       <c r="B3">
         <v>9</v>
@@ -18000,7 +17958,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>611</v>
+        <v>597</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -18017,7 +17975,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>612</v>
+        <v>598</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -18034,7 +17992,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>613</v>
+        <v>599</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -18051,7 +18009,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>614</v>
+        <v>600</v>
       </c>
       <c r="B7">
         <v>7</v>
@@ -18068,7 +18026,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>615</v>
+        <v>601</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -18085,7 +18043,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -18102,7 +18060,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>617</v>
+        <v>603</v>
       </c>
       <c r="B10">
         <v>11</v>
@@ -18119,7 +18077,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>618</v>
+        <v>604</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -18136,7 +18094,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -18153,7 +18111,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>620</v>
+        <v>606</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -18170,7 +18128,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -18187,7 +18145,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -18204,7 +18162,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>623</v>
+        <v>609</v>
       </c>
       <c r="B16">
         <v>5</v>
@@ -18221,7 +18179,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
       <c r="B17">
         <v>6</v>
@@ -18238,7 +18196,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>625</v>
+        <v>611</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -18255,7 +18213,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>626</v>
+        <v>612</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -18272,7 +18230,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -18289,7 +18247,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -18306,7 +18264,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="B22">
         <v>10</v>
@@ -18323,7 +18281,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -18340,7 +18298,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -18357,7 +18315,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>630</v>
+        <v>616</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -18374,7 +18332,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -18391,7 +18349,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -18408,7 +18366,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>633</v>
+        <v>619</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -18425,7 +18383,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>634</v>
+        <v>620</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -18442,7 +18400,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>635</v>
+        <v>621</v>
       </c>
       <c r="B30">
         <v>3</v>
@@ -18459,7 +18417,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="B31">
         <v>3</v>
@@ -18476,7 +18434,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -18493,7 +18451,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -18510,7 +18468,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -18527,7 +18485,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -18544,7 +18502,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -18561,7 +18519,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>642</v>
+        <v>628</v>
       </c>
       <c r="B37">
         <v>4</v>
@@ -18578,7 +18536,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="B38">
         <v>4</v>
@@ -18595,7 +18553,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -18612,7 +18570,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>645</v>
+        <v>631</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -18629,7 +18587,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="B41">
         <v>4</v>
@@ -18646,7 +18604,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="B42">
         <v>4</v>
@@ -18663,7 +18621,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B43">
         <v>14</v>
@@ -18680,7 +18638,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="B44">
         <v>13</v>
@@ -18697,7 +18655,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="B45">
         <v>14</v>
@@ -18714,7 +18672,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="B46">
         <v>10</v>
@@ -18731,7 +18689,7 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="B47">
         <v>5</v>
@@ -18748,7 +18706,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="B48">
         <v>7</v>
@@ -18765,7 +18723,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="B49">
         <v>5</v>
@@ -18782,7 +18740,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>651</v>
+        <v>637</v>
       </c>
       <c r="B50">
         <v>5</v>
@@ -18799,7 +18757,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="B51">
         <v>5</v>
@@ -18816,7 +18774,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="B52">
         <v>6</v>
@@ -18833,7 +18791,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>653</v>
+        <v>639</v>
       </c>
       <c r="B53">
         <v>5</v>
@@ -18850,7 +18808,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="B54">
         <v>6</v>
@@ -18867,7 +18825,7 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>655</v>
+        <v>641</v>
       </c>
       <c r="B55">
         <v>6</v>
@@ -18884,7 +18842,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="B56">
         <v>6</v>
@@ -18901,7 +18859,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>657</v>
+        <v>643</v>
       </c>
       <c r="B57">
         <v>5</v>
@@ -18918,7 +18876,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>658</v>
+        <v>644</v>
       </c>
       <c r="B58">
         <v>6</v>
@@ -18935,7 +18893,7 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>659</v>
+        <v>645</v>
       </c>
       <c r="B59">
         <v>6</v>
@@ -18952,7 +18910,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>660</v>
+        <v>646</v>
       </c>
       <c r="B60">
         <v>8</v>
@@ -18969,7 +18927,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>661</v>
+        <v>647</v>
       </c>
       <c r="B61">
         <v>8</v>
@@ -18986,7 +18944,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>662</v>
+        <v>648</v>
       </c>
       <c r="B62">
         <v>3</v>
@@ -19003,7 +18961,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="B63">
         <v>8</v>
@@ -19020,7 +18978,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="B64">
         <v>8</v>
@@ -19037,7 +18995,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>665</v>
+        <v>651</v>
       </c>
       <c r="B65">
         <v>8</v>
@@ -19054,7 +19012,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>666</v>
+        <v>652</v>
       </c>
       <c r="B66">
         <v>8</v>
@@ -19071,7 +19029,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="B67">
         <v>6</v>
@@ -19088,7 +19046,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="B68">
         <v>8</v>
@@ -19105,7 +19063,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="B69">
         <v>8</v>
@@ -19122,7 +19080,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="B70">
         <v>9</v>
@@ -19139,7 +19097,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="B71">
         <v>9</v>
@@ -19156,7 +19114,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="B72">
         <v>9</v>
@@ -19173,7 +19131,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="B73">
         <v>9</v>
@@ -19190,7 +19148,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="B74">
         <v>9</v>
@@ -19207,7 +19165,7 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="B75">
         <v>9</v>
@@ -19224,7 +19182,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="B76">
         <v>9</v>
@@ -19241,7 +19199,7 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="B77">
         <v>13</v>
@@ -19258,7 +19216,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="B78">
         <v>7</v>
@@ -19275,7 +19233,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="B79">
         <v>10</v>
@@ -19292,7 +19250,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="B80">
         <v>10</v>
@@ -19309,7 +19267,7 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B81">
         <v>10</v>
@@ -19326,7 +19284,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="B82">
         <v>10</v>
@@ -19343,7 +19301,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B83">
         <v>10</v>
@@ -19360,7 +19318,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="B84">
         <v>10</v>
@@ -19377,7 +19335,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="B85">
         <v>11</v>
@@ -19394,7 +19352,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="B86">
         <v>11</v>
@@ -19411,7 +19369,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="B87">
         <v>11</v>
@@ -19428,7 +19386,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="B88">
         <v>11</v>
@@ -19445,7 +19403,7 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="B89">
         <v>11</v>
@@ -19462,7 +19420,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="B90">
         <v>11</v>
@@ -19479,7 +19437,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="B91">
         <v>11</v>
@@ -19496,7 +19454,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="B92">
         <v>12</v>
@@ -19513,7 +19471,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="B93">
         <v>12</v>
@@ -19530,7 +19488,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="B94">
         <v>12</v>
@@ -19547,7 +19505,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="B95">
         <v>12</v>
@@ -19564,7 +19522,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="B96">
         <v>12</v>
@@ -19581,7 +19539,7 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="B97">
         <v>12</v>
@@ -19598,7 +19556,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="B98">
         <v>12</v>
@@ -19615,7 +19573,7 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="B99">
         <v>12</v>
@@ -19632,7 +19590,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="B100">
         <v>4</v>
@@ -19649,7 +19607,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="B101">
         <v>13</v>
@@ -19666,7 +19624,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="B102">
         <v>13</v>
@@ -19683,7 +19641,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="B103">
         <v>13</v>
@@ -19700,7 +19658,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="B104">
         <v>13</v>
@@ -19717,7 +19675,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="B105">
         <v>13</v>
@@ -19734,7 +19692,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="B106">
         <v>13</v>
@@ -19751,7 +19709,7 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="B107">
         <v>14</v>
@@ -19768,7 +19726,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="B108">
         <v>14</v>
@@ -19785,7 +19743,7 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="B109">
         <v>2</v>
@@ -19802,7 +19760,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="B110">
         <v>14</v>
@@ -19819,7 +19777,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="B111">
         <v>14</v>
@@ -19836,7 +19794,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="B112">
         <v>14</v>
@@ -19853,7 +19811,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="B113">
         <v>14</v>
@@ -21952,8 +21910,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>546</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2">
         <v>14</v>
@@ -21977,8 +21935,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>547</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -22002,8 +21960,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>548</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -22027,8 +21985,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>549</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5">
         <v>9</v>
@@ -22052,8 +22010,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>550</v>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -22077,8 +22035,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>551</v>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7">
         <v>13</v>
@@ -22102,8 +22060,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>552</v>
+      <c r="A8">
+        <v>7</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -22127,8 +22085,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>553</v>
+      <c r="A9">
+        <v>8</v>
       </c>
       <c r="B9">
         <v>14</v>
@@ -22152,8 +22110,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>554</v>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -22177,8 +22135,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>555</v>
+      <c r="A11">
+        <v>10</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -22202,8 +22160,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>556</v>
+      <c r="A12">
+        <v>11</v>
       </c>
       <c r="B12">
         <v>9</v>
@@ -22227,8 +22185,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>557</v>
+      <c r="A13">
+        <v>12</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -22252,8 +22210,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>558</v>
+      <c r="A14">
+        <v>13</v>
       </c>
       <c r="B14">
         <v>13</v>
@@ -22277,8 +22235,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>559</v>
+      <c r="A15">
+        <v>14</v>
       </c>
       <c r="B15">
         <v>7</v>
@@ -22322,19 +22280,19 @@
         <v>512</v>
       </c>
       <c r="C1" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="D1" t="s">
         <v>514</v>
       </c>
       <c r="E1" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="F1" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="G1" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="H1" t="s">
         <v>23</v>
@@ -22354,10 +22312,10 @@
         <v>520</v>
       </c>
       <c r="C2" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D2" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -22366,10 +22324,10 @@
         <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H2" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -22380,10 +22338,10 @@
         <v>520</v>
       </c>
       <c r="C3" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D3" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -22392,10 +22350,10 @@
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H3" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -22406,10 +22364,10 @@
         <v>518</v>
       </c>
       <c r="C4" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D4" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -22418,10 +22376,10 @@
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H4" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -22432,10 +22390,10 @@
         <v>518</v>
       </c>
       <c r="C5" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D5" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -22444,10 +22402,10 @@
         <v>5</v>
       </c>
       <c r="G5" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H5" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -22458,10 +22416,10 @@
         <v>518</v>
       </c>
       <c r="C6" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D6" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -22470,10 +22428,10 @@
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H6" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -22484,10 +22442,10 @@
         <v>518</v>
       </c>
       <c r="C7" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D7" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E7">
         <v>14</v>
@@ -22496,10 +22454,10 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H7" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -22510,10 +22468,10 @@
         <v>518</v>
       </c>
       <c r="C8" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D8" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -22522,10 +22480,10 @@
         <v>7</v>
       </c>
       <c r="G8" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="H8" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -22536,10 +22494,10 @@
         <v>518</v>
       </c>
       <c r="C9" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D9" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E9">
         <v>7</v>
@@ -22548,10 +22506,10 @@
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="H9" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -22562,10 +22520,10 @@
         <v>518</v>
       </c>
       <c r="C10" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D10" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -22574,10 +22532,10 @@
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H10" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -22588,10 +22546,10 @@
         <v>518</v>
       </c>
       <c r="C11" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D11" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E11">
         <v>14</v>
@@ -22600,10 +22558,10 @@
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H11" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -22614,10 +22572,10 @@
         <v>518</v>
       </c>
       <c r="C12" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D12" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E12">
         <v>14</v>
@@ -22626,10 +22584,10 @@
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H12" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -22640,10 +22598,10 @@
         <v>518</v>
       </c>
       <c r="C13" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D13" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E13">
         <v>13</v>
@@ -22652,10 +22610,10 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H13" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -22666,10 +22624,10 @@
         <v>518</v>
       </c>
       <c r="C14" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D14" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E14">
         <v>14</v>
@@ -22678,10 +22636,10 @@
         <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="H14" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -22692,10 +22650,10 @@
         <v>518</v>
       </c>
       <c r="C15" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D15" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E15">
         <v>11</v>
@@ -22704,10 +22662,10 @@
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="H15" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -22718,10 +22676,10 @@
         <v>518</v>
       </c>
       <c r="C16" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D16" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E16">
         <v>14</v>
@@ -22730,10 +22688,10 @@
         <v>6</v>
       </c>
       <c r="G16" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="H16" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -22744,10 +22702,10 @@
         <v>518</v>
       </c>
       <c r="C17" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D17" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E17">
         <v>6</v>
@@ -22756,10 +22714,10 @@
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="H17" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -22770,10 +22728,10 @@
         <v>518</v>
       </c>
       <c r="C18" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D18" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E18">
         <v>13</v>
@@ -22782,10 +22740,10 @@
         <v>5</v>
       </c>
       <c r="G18" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H18" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -22796,10 +22754,10 @@
         <v>518</v>
       </c>
       <c r="C19" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D19" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -22808,10 +22766,10 @@
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H19" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -22822,10 +22780,10 @@
         <v>518</v>
       </c>
       <c r="C20" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D20" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E20">
         <v>14</v>
@@ -22834,10 +22792,10 @@
         <v>5</v>
       </c>
       <c r="G20" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H20" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -22848,10 +22806,10 @@
         <v>518</v>
       </c>
       <c r="C21" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D21" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -22860,10 +22818,10 @@
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H21" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -22874,10 +22832,10 @@
         <v>518</v>
       </c>
       <c r="C22" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D22" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -22886,10 +22844,10 @@
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H22" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -22900,10 +22858,10 @@
         <v>518</v>
       </c>
       <c r="C23" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D23" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -22912,10 +22870,10 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H23" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -22926,10 +22884,10 @@
         <v>522</v>
       </c>
       <c r="C24" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D24" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -22938,10 +22896,10 @@
         <v>5</v>
       </c>
       <c r="G24" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H24" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -22952,10 +22910,10 @@
         <v>522</v>
       </c>
       <c r="C25" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D25" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E25">
         <v>13</v>
@@ -22964,10 +22922,10 @@
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="H25" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -22978,10 +22936,10 @@
         <v>522</v>
       </c>
       <c r="C26" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D26" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E26">
         <v>14</v>
@@ -22990,10 +22948,10 @@
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H26" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -23004,10 +22962,10 @@
         <v>522</v>
       </c>
       <c r="C27" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D27" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E27">
         <v>5</v>
@@ -23016,10 +22974,10 @@
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H27" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -23030,10 +22988,10 @@
         <v>521</v>
       </c>
       <c r="C28" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D28" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E28">
         <v>14</v>
@@ -23042,10 +23000,10 @@
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="H28" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -23056,10 +23014,10 @@
         <v>522</v>
       </c>
       <c r="C29" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D29" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -23068,10 +23026,10 @@
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="H29" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -23082,10 +23040,10 @@
         <v>523</v>
       </c>
       <c r="C30" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D30" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E30">
         <v>5</v>
@@ -23094,10 +23052,10 @@
         <v>538</v>
       </c>
       <c r="G30" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="H30" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -23108,10 +23066,10 @@
         <v>523</v>
       </c>
       <c r="C31" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D31" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="E31">
         <v>13</v>
@@ -23120,10 +23078,10 @@
         <v>538</v>
       </c>
       <c r="G31" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="H31" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -23131,13 +23089,13 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="C32" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D32" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -23146,10 +23104,10 @@
         <v>1</v>
       </c>
       <c r="G32" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H32" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -23157,13 +23115,13 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="C33" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D33" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -23172,10 +23130,10 @@
         <v>1</v>
       </c>
       <c r="G33" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H33" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -23186,10 +23144,10 @@
         <v>522</v>
       </c>
       <c r="C34" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D34" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -23198,10 +23156,10 @@
         <v>7</v>
       </c>
       <c r="G34" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H34" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -23209,13 +23167,13 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="C35" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D35" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -23224,10 +23182,10 @@
         <v>5</v>
       </c>
       <c r="G35" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H35" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -23238,10 +23196,10 @@
         <v>522</v>
       </c>
       <c r="C36" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D36" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E36">
         <v>7</v>
@@ -23250,10 +23208,10 @@
         <v>7</v>
       </c>
       <c r="G36" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H36" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -23264,10 +23222,10 @@
         <v>521</v>
       </c>
       <c r="C37" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="D37" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -23276,10 +23234,10 @@
         <v>2</v>
       </c>
       <c r="G37" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H37" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -23287,13 +23245,13 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="C38" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D38" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E38">
         <v>7</v>
@@ -23302,10 +23260,10 @@
         <v>7</v>
       </c>
       <c r="G38" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H38" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -23313,13 +23271,13 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="C39" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D39" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E39">
         <v>7</v>
@@ -23328,10 +23286,10 @@
         <v>7</v>
       </c>
       <c r="G39" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H39" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -23339,13 +23297,13 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="C40" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="D40" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -23354,10 +23312,10 @@
         <v>13</v>
       </c>
       <c r="G40" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H40" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -23365,22 +23323,22 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="C41" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="D41" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E41">
         <v>6</v>
       </c>
       <c r="G41" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H41" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -23391,22 +23349,22 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="C42" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
       <c r="D42" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E42">
         <v>7</v>
       </c>
       <c r="G42" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H42" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="J42">
         <v>2</v>
@@ -23417,13 +23375,13 @@
         <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
       <c r="C43" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
       <c r="D43" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -23432,10 +23390,10 @@
         <v>6</v>
       </c>
       <c r="G43" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="H43" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="J43">
         <v>3</v>
@@ -23483,13 +23441,13 @@
         <v>532</v>
       </c>
       <c r="L1" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="M1" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
       <c r="N1" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -23497,13 +23455,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="C2" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D2" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -23518,7 +23476,7 @@
         <v>538</v>
       </c>
       <c r="I2" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -23526,13 +23484,13 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="C3" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D3" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -23547,7 +23505,7 @@
         <v>538</v>
       </c>
       <c r="I3" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -23555,13 +23513,13 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="C4" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D4" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -23576,7 +23534,7 @@
         <v>538</v>
       </c>
       <c r="I4" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -23584,13 +23542,13 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="C5" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D5" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -23605,7 +23563,7 @@
         <v>538</v>
       </c>
       <c r="I5" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -23616,7 +23574,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D6">
         <v>9</v>
@@ -23628,13 +23586,13 @@
         <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H6" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I6" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -23645,7 +23603,7 @@
         <v>219</v>
       </c>
       <c r="C7" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D7">
         <v>219</v>
@@ -23657,13 +23615,13 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H7" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I7" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -23674,7 +23632,7 @@
         <v>220</v>
       </c>
       <c r="C8" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D8">
         <v>220</v>
@@ -23686,13 +23644,13 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H8" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I8" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -23703,7 +23661,7 @@
         <v>194</v>
       </c>
       <c r="C9" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D9">
         <v>194</v>
@@ -23715,13 +23673,13 @@
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H9" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I9" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -23732,7 +23690,7 @@
         <v>158</v>
       </c>
       <c r="C10" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D10">
         <v>158</v>
@@ -23744,13 +23702,13 @@
         <v>7</v>
       </c>
       <c r="G10" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H10" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I10" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -23761,7 +23719,7 @@
         <v>247</v>
       </c>
       <c r="C11" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D11">
         <v>247</v>
@@ -23773,13 +23731,13 @@
         <v>7</v>
       </c>
       <c r="G11" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H11" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I11" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -23790,7 +23748,7 @@
         <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D12">
         <v>88</v>
@@ -23802,13 +23760,13 @@
         <v>7</v>
       </c>
       <c r="G12" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H12" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I12" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -23819,7 +23777,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -23831,13 +23789,13 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H13" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I13" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -23848,7 +23806,7 @@
         <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D14">
         <v>152</v>
@@ -23860,13 +23818,13 @@
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H14" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I14" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -23874,13 +23832,13 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="C15" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D15" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="E15">
         <v>5</v>
@@ -23895,7 +23853,7 @@
         <v>538</v>
       </c>
       <c r="I15" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -23903,13 +23861,13 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="C16" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D16" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="E16">
         <v>14</v>
@@ -23924,7 +23882,7 @@
         <v>538</v>
       </c>
       <c r="I16" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -23932,13 +23890,13 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="C17" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D17" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="E17">
         <v>14</v>
@@ -23953,7 +23911,7 @@
         <v>538</v>
       </c>
       <c r="I17" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -23961,13 +23919,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="C18" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D18" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="E18">
         <v>14</v>
@@ -23982,7 +23940,7 @@
         <v>538</v>
       </c>
       <c r="I18" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -23993,7 +23951,7 @@
         <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D19">
         <v>73</v>
@@ -24005,13 +23963,13 @@
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H19" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I19" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -24022,7 +23980,7 @@
         <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D20">
         <v>241</v>
@@ -24034,13 +23992,13 @@
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H20" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I20" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -24051,7 +24009,7 @@
         <v>121</v>
       </c>
       <c r="C21" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D21">
         <v>121</v>
@@ -24063,13 +24021,13 @@
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H21" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I21" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -24080,7 +24038,7 @@
         <v>177</v>
       </c>
       <c r="C22" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D22">
         <v>177</v>
@@ -24092,13 +24050,13 @@
         <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H22" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I22" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -24109,7 +24067,7 @@
         <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D23">
         <v>66</v>
@@ -24121,13 +24079,13 @@
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H23" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I23" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -24138,7 +24096,7 @@
         <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D24">
         <v>145</v>
@@ -24150,13 +24108,13 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H24" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I24" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -24167,7 +24125,7 @@
         <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D25">
         <v>56</v>
@@ -24179,13 +24137,13 @@
         <v>6</v>
       </c>
       <c r="G25" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H25" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I25" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -24196,7 +24154,7 @@
         <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D26">
         <v>93</v>
@@ -24208,13 +24166,13 @@
         <v>6</v>
       </c>
       <c r="G26" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H26" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I26" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -24225,7 +24183,7 @@
         <v>161</v>
       </c>
       <c r="C27" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D27">
         <v>161</v>
@@ -24237,13 +24195,13 @@
         <v>6</v>
       </c>
       <c r="G27" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H27" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I27" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -24251,13 +24209,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="C28" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D28" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="E28">
         <v>14</v>
@@ -24272,7 +24230,7 @@
         <v>538</v>
       </c>
       <c r="I28" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -24280,13 +24238,13 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="C29" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D29" t="s">
-        <v>597</v>
+        <v>583</v>
       </c>
       <c r="E29">
         <v>13</v>
@@ -24301,7 +24259,7 @@
         <v>538</v>
       </c>
       <c r="I29" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -24309,13 +24267,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="C30" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D30" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="E30">
         <v>13</v>
@@ -24330,7 +24288,7 @@
         <v>538</v>
       </c>
       <c r="I30" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -24338,13 +24296,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="C31" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D31" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
       <c r="E31">
         <v>5</v>
@@ -24359,7 +24317,7 @@
         <v>538</v>
       </c>
       <c r="I31" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -24370,7 +24328,7 @@
         <v>409</v>
       </c>
       <c r="C32" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D32">
         <v>409</v>
@@ -24382,13 +24340,13 @@
         <v>5</v>
       </c>
       <c r="G32" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H32" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I32" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -24399,7 +24357,7 @@
         <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D33">
         <v>48</v>
@@ -24411,13 +24369,13 @@
         <v>5</v>
       </c>
       <c r="G33" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H33" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I33" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -24428,7 +24386,7 @@
         <v>414</v>
       </c>
       <c r="C34" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D34">
         <v>414</v>
@@ -24440,13 +24398,13 @@
         <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H34" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I34" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -24457,7 +24415,7 @@
         <v>238</v>
       </c>
       <c r="C35" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D35">
         <v>238</v>
@@ -24469,13 +24427,13 @@
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H35" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I35" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -24486,7 +24444,7 @@
         <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D36">
         <v>133</v>
@@ -24498,13 +24456,13 @@
         <v>5</v>
       </c>
       <c r="G36" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H36" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I36" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -24515,7 +24473,7 @@
         <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D37">
         <v>143</v>
@@ -24527,13 +24485,13 @@
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H37" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I37" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -24544,7 +24502,7 @@
         <v>72</v>
       </c>
       <c r="C38" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D38">
         <v>72</v>
@@ -24556,13 +24514,13 @@
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H38" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I38" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -24573,7 +24531,7 @@
         <v>219</v>
       </c>
       <c r="C39" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D39">
         <v>219</v>
@@ -24585,13 +24543,13 @@
         <v>2</v>
       </c>
       <c r="G39" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H39" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I39" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -24602,7 +24560,7 @@
         <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D40">
         <v>49</v>
@@ -24614,13 +24572,13 @@
         <v>2</v>
       </c>
       <c r="G40" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H40" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I40" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -24628,13 +24586,13 @@
         <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="C41" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D41" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
       <c r="E41">
         <v>5</v>
@@ -24649,7 +24607,7 @@
         <v>538</v>
       </c>
       <c r="I41" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -24660,7 +24618,7 @@
         <v>92</v>
       </c>
       <c r="C42" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D42">
         <v>92</v>
@@ -24672,13 +24630,13 @@
         <v>5</v>
       </c>
       <c r="G42" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H42" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I42" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -24689,7 +24647,7 @@
         <v>241</v>
       </c>
       <c r="C43" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D43">
         <v>241</v>
@@ -24701,13 +24659,13 @@
         <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H43" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I43" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
@@ -24718,7 +24676,7 @@
         <v>259</v>
       </c>
       <c r="C44" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D44">
         <v>259</v>
@@ -24730,13 +24688,13 @@
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H44" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I44" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -24747,7 +24705,7 @@
         <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D45">
         <v>133</v>
@@ -24759,13 +24717,13 @@
         <v>5</v>
       </c>
       <c r="G45" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H45" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I45" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -24776,7 +24734,7 @@
         <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D46">
         <v>139</v>
@@ -24788,13 +24746,13 @@
         <v>5</v>
       </c>
       <c r="G46" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="H46" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I46" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -24805,7 +24763,7 @@
         <v>273</v>
       </c>
       <c r="C47" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D47">
         <v>273</v>
@@ -24817,13 +24775,13 @@
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="H47" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I47" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -24834,7 +24792,7 @@
         <v>49</v>
       </c>
       <c r="C48" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D48">
         <v>49</v>
@@ -24846,13 +24804,13 @@
         <v>2</v>
       </c>
       <c r="G48" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H48" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I48" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -24863,7 +24821,7 @@
         <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D49">
         <v>8</v>
@@ -24875,13 +24833,13 @@
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H49" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I49" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -24892,7 +24850,7 @@
         <v>290</v>
       </c>
       <c r="C50" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D50">
         <v>290</v>
@@ -24904,13 +24862,13 @@
         <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H50" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="I50" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -24921,7 +24879,7 @@
         <v>209</v>
       </c>
       <c r="C51" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D51">
         <v>209</v>
@@ -24933,16 +24891,16 @@
         <v>538</v>
       </c>
       <c r="G51" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H51" t="s">
         <v>538</v>
       </c>
       <c r="I51" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="J51" t="s">
-        <v>600</v>
+        <v>586</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -24953,7 +24911,7 @@
         <v>94</v>
       </c>
       <c r="C52" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D52">
         <v>94</v>
@@ -24965,16 +24923,16 @@
         <v>538</v>
       </c>
       <c r="G52" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="H52" t="s">
         <v>538</v>
       </c>
       <c r="I52" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="J52" t="s">
-        <v>601</v>
+        <v>587</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -24985,7 +24943,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D53">
         <v>420</v>
@@ -25003,7 +24961,7 @@
         <v>534</v>
       </c>
       <c r="I53" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -25014,10 +24972,10 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D54" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="E54">
         <v>6</v>
@@ -25026,7 +24984,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -25037,7 +24995,7 @@
         <v>3</v>
       </c>
       <c r="C55" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D55">
         <v>419</v>
@@ -25055,7 +25013,7 @@
         <v>534</v>
       </c>
       <c r="I55" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
@@ -25066,10 +25024,10 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D56" t="s">
-        <v>602</v>
+        <v>588</v>
       </c>
       <c r="E56">
         <v>6</v>
@@ -25078,7 +25036,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
@@ -25089,7 +25047,7 @@
         <v>4</v>
       </c>
       <c r="C57" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D57">
         <v>421</v>
@@ -25107,7 +25065,7 @@
         <v>537</v>
       </c>
       <c r="I57" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -25118,7 +25076,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D58">
         <v>130</v>
@@ -25136,7 +25094,7 @@
         <v>534</v>
       </c>
       <c r="I58" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -25147,10 +25105,10 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D59" t="s">
-        <v>598</v>
+        <v>584</v>
       </c>
       <c r="E59">
         <v>5</v>
@@ -25159,7 +25117,7 @@
         <v>7</v>
       </c>
       <c r="I59" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -25170,10 +25128,10 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D60" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="E60">
         <v>5</v>
@@ -25182,7 +25140,7 @@
         <v>7</v>
       </c>
       <c r="I60" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -25193,7 +25151,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D61">
         <v>49</v>
@@ -25205,13 +25163,13 @@
         <v>2</v>
       </c>
       <c r="G61" t="s">
-        <v>599</v>
+        <v>585</v>
       </c>
       <c r="H61" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
       <c r="I61" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -25222,7 +25180,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D62">
         <v>423</v>
@@ -25240,7 +25198,7 @@
         <v>537</v>
       </c>
       <c r="I62" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
@@ -25251,7 +25209,7 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D63">
         <v>435</v>
@@ -25269,7 +25227,7 @@
         <v>537</v>
       </c>
       <c r="I63" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
@@ -25280,7 +25238,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D64">
         <v>437</v>
@@ -25298,7 +25256,7 @@
         <v>537</v>
       </c>
       <c r="I64" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
@@ -25309,7 +25267,7 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D65">
         <v>434</v>
@@ -25327,7 +25285,7 @@
         <v>537</v>
       </c>
       <c r="I65" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -25338,7 +25296,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D66">
         <v>437</v>
@@ -25356,7 +25314,7 @@
         <v>534</v>
       </c>
       <c r="I66" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -25367,7 +25325,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D67">
         <v>437</v>
@@ -25385,7 +25343,7 @@
         <v>537</v>
       </c>
       <c r="I67" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -25396,7 +25354,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D68">
         <v>434</v>
@@ -25414,7 +25372,7 @@
         <v>534</v>
       </c>
       <c r="I68" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -25425,10 +25383,10 @@
         <v>1</v>
       </c>
       <c r="C69" t="s">
+        <v>575</v>
+      </c>
+      <c r="D69" t="s">
         <v>589</v>
-      </c>
-      <c r="D69" t="s">
-        <v>603</v>
       </c>
       <c r="E69">
         <v>2</v>
@@ -25437,7 +25395,7 @@
         <v>13</v>
       </c>
       <c r="I69" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -25448,10 +25406,10 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="D70" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="E70">
         <v>13</v>
@@ -25460,7 +25418,7 @@
         <v>2</v>
       </c>
       <c r="I70" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -25471,7 +25429,7 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D71">
         <v>93</v>
@@ -25483,7 +25441,7 @@
         <v>534</v>
       </c>
       <c r="I71" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -25494,7 +25452,7 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D72">
         <v>158</v>
@@ -25506,7 +25464,7 @@
         <v>534</v>
       </c>
       <c r="I72" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -25517,7 +25475,7 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D73">
         <v>419</v>
@@ -25543,7 +25501,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="D74">
         <v>444</v>

--- a/Fantasy unificado/roster.xlsx
+++ b/Fantasy unificado/roster.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Evolucoes/Fantasy unificado/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/db44bf30ba5480d8/Documentos/Python Scripts/Fantasy/Fantasy unificado/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8CEADB7-D625-4CA9-8123-BD4FA2F3FDF8}"/>
+  <xr:revisionPtr revIDLastSave="350" documentId="11_C9A9D9B2D1F41C577D71D6D20FCB10DCD9AF004A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3EA1D77-A540-40BF-A4A6-6F1074C29FD7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="players" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="699">
   <si>
     <t>team_id</t>
   </si>
@@ -2140,6 +2140,9 @@
   </si>
   <si>
     <t>P2029_R2_T14</t>
+  </si>
+  <si>
+    <t>rodada</t>
   </si>
 </sst>
 </file>
@@ -21875,7 +21878,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H274"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -21886,7 +21889,7 @@
     <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>539</v>
       </c>
@@ -21908,8 +21911,11 @@
       <c r="G1" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -21920,12 +21926,6 @@
         <f>VLOOKUP(B2,teams!$A$1:$B$15,2)</f>
         <v>Tchêltics da Peleia</v>
       </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
       <c r="F2">
         <v>5</v>
       </c>
@@ -21933,8 +21933,11 @@
         <f>VLOOKUP(F2,teams!$A$1:$B$15,2)</f>
         <v>Kaipiras da Gema</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -21945,12 +21948,6 @@
         <f>VLOOKUP(B3,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
       <c r="F3">
         <v>1</v>
       </c>
@@ -21958,8 +21955,11 @@
         <f>VLOOKUP(F3,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -21970,12 +21970,6 @@
         <f>VLOOKUP(B4,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
       <c r="F4">
         <v>4</v>
       </c>
@@ -21983,8 +21977,11 @@
         <f>VLOOKUP(F4,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -21995,12 +21992,6 @@
         <f>VLOOKUP(B5,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
       <c r="F5">
         <v>2</v>
       </c>
@@ -22008,8 +21999,11 @@
         <f>VLOOKUP(F5,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -22020,12 +22014,6 @@
         <f>VLOOKUP(B6,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
       <c r="F6">
         <v>12</v>
       </c>
@@ -22033,8 +22021,11 @@
         <f>VLOOKUP(F6,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -22045,12 +22036,6 @@
         <f>VLOOKUP(B7,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
       <c r="F7">
         <v>11</v>
       </c>
@@ -22058,8 +22043,11 @@
         <f>VLOOKUP(F7,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -22070,12 +22058,6 @@
         <f>VLOOKUP(B8,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
       <c r="F8">
         <v>10</v>
       </c>
@@ -22083,8 +22065,11 @@
         <f>VLOOKUP(F8,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -22095,12 +22080,6 @@
         <f>VLOOKUP(B9,teams!$A$1:$B$15,2)</f>
         <v>Tchêltics da Peleia</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>5</v>
-      </c>
       <c r="F9">
         <v>6</v>
       </c>
@@ -22108,8 +22087,12 @@
         <f>VLOOKUP(F9,teams!$A$1:$B$15,2)</f>
         <v>Miami Barons</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <f t="shared" ref="H9:H29" si="0">H2+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -22120,12 +22103,6 @@
         <f>VLOOKUP(B10,teams!$A$1:$B$15,2)</f>
         <v>Kaipiras da Gema</v>
       </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>6</v>
-      </c>
       <c r="F10">
         <v>10</v>
       </c>
@@ -22133,8 +22110,12 @@
         <f>VLOOKUP(F10,teams!$A$1:$B$15,2)</f>
         <v>Pelotas Vikings</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -22145,12 +22126,6 @@
         <f>VLOOKUP(B11,teams!$A$1:$B$15,2)</f>
         <v>New Orleans Dancers</v>
       </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>3</v>
-      </c>
       <c r="F11">
         <v>1</v>
       </c>
@@ -22158,8 +22133,12 @@
         <f>VLOOKUP(F11,teams!$A$1:$B$15,2)</f>
         <v>Alabama Black Bears</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -22170,12 +22149,6 @@
         <f>VLOOKUP(B12,teams!$A$1:$B$15,2)</f>
         <v>Osasco Heat</v>
       </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>4</v>
-      </c>
       <c r="F12">
         <v>4</v>
       </c>
@@ -22183,8 +22156,12 @@
         <f>VLOOKUP(F12,teams!$A$1:$B$15,2)</f>
         <v>Itajubá Rabbits</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -22195,12 +22172,6 @@
         <f>VLOOKUP(B13,teams!$A$1:$B$15,2)</f>
         <v>Guarulhos Nuggets</v>
       </c>
-      <c r="D13">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>3</v>
-      </c>
       <c r="F13">
         <v>2</v>
       </c>
@@ -22208,8 +22179,12 @@
         <f>VLOOKUP(F13,teams!$A$1:$B$15,2)</f>
         <v>Franca Celtics</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -22220,12 +22195,6 @@
         <f>VLOOKUP(B14,teams!$A$1:$B$15,2)</f>
         <v>RJ Black Mamba</v>
       </c>
-      <c r="D14">
-        <v>6</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
       <c r="F14">
         <v>12</v>
       </c>
@@ -22233,8 +22202,12 @@
         <f>VLOOKUP(F14,teams!$A$1:$B$15,2)</f>
         <v>Recife Black Diamond</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -22245,18 +22218,5973 @@
         <f>VLOOKUP(B15,teams!$A$1:$B$15,2)</f>
         <v>Montreal Turtles</v>
       </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
       <c r="F15">
         <v>11</v>
       </c>
       <c r="G15" t="str">
         <f>VLOOKUP(F15,teams!$A$1:$B$15,2)</f>
         <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" t="str">
+        <f>VLOOKUP(B16,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16" t="str">
+        <f>VLOOKUP(F16,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17" t="str">
+        <f>VLOOKUP(B17,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F17">
+        <v>8</v>
+      </c>
+      <c r="G17" t="str">
+        <f>VLOOKUP(F17,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+      <c r="C18" t="str">
+        <f>VLOOKUP(B18,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18" t="str">
+        <f>VLOOKUP(F18,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+      <c r="C19" t="str">
+        <f>VLOOKUP(B19,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <f>VLOOKUP(F19,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>11</v>
+      </c>
+      <c r="C20" t="str">
+        <f>VLOOKUP(B20,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20" t="str">
+        <f>VLOOKUP(F20,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>13</v>
+      </c>
+      <c r="C21" t="str">
+        <f>VLOOKUP(B21,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" t="str">
+        <f>VLOOKUP(F21,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22" t="str">
+        <f>VLOOKUP(B22,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F22">
+        <v>12</v>
+      </c>
+      <c r="G22" t="str">
+        <f>VLOOKUP(F22,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23" t="str">
+        <f>VLOOKUP(B23,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F23">
+        <v>8</v>
+      </c>
+      <c r="G23" t="str">
+        <f>VLOOKUP(F23,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>14</v>
+      </c>
+      <c r="C24" t="str">
+        <f>VLOOKUP(B24,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24" t="str">
+        <f>VLOOKUP(F24,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="str">
+        <f>VLOOKUP(B25,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="str">
+        <f>VLOOKUP(F25,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>11</v>
+      </c>
+      <c r="C26" t="str">
+        <f>VLOOKUP(B26,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F26">
+        <v>12</v>
+      </c>
+      <c r="G26" t="str">
+        <f>VLOOKUP(F26,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" t="str">
+        <f>VLOOKUP(B27,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F27">
+        <v>10</v>
+      </c>
+      <c r="G27" t="str">
+        <f>VLOOKUP(F27,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>4</v>
+      </c>
+      <c r="C28" t="str">
+        <f>VLOOKUP(B28,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F28">
+        <v>13</v>
+      </c>
+      <c r="G28" t="str">
+        <f>VLOOKUP(F28,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29" t="str">
+        <f>VLOOKUP(B29,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29" t="str">
+        <f>VLOOKUP(F29,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>5</v>
+      </c>
+      <c r="C30" t="str">
+        <f>VLOOKUP(B30,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F30">
+        <v>9</v>
+      </c>
+      <c r="G30" t="str">
+        <f>VLOOKUP(F30,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="H30">
+        <f>H23+1</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>14</v>
+      </c>
+      <c r="C31" t="str">
+        <f>VLOOKUP(B31,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31" t="str">
+        <f>VLOOKUP(F31,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H31">
+        <f t="shared" ref="H31:H94" si="1">H24+1</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32" t="str">
+        <f>VLOOKUP(B32,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32" t="str">
+        <f>VLOOKUP(F32,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33" t="str">
+        <f>VLOOKUP(B33,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F33">
+        <v>4</v>
+      </c>
+      <c r="G33" t="str">
+        <f>VLOOKUP(F33,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>11</v>
+      </c>
+      <c r="C34" t="str">
+        <f>VLOOKUP(B34,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34" t="str">
+        <f>VLOOKUP(F34,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>13</v>
+      </c>
+      <c r="C35" t="str">
+        <f>VLOOKUP(B35,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35" t="str">
+        <f>VLOOKUP(F35,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>10</v>
+      </c>
+      <c r="C36" t="str">
+        <f>VLOOKUP(B36,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F36">
+        <v>12</v>
+      </c>
+      <c r="G36" t="str">
+        <f>VLOOKUP(F36,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>5</v>
+      </c>
+      <c r="C37" t="str">
+        <f>VLOOKUP(B37,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" t="str">
+        <f>VLOOKUP(F37,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>14</v>
+      </c>
+      <c r="C38" t="str">
+        <f>VLOOKUP(B38,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F38">
+        <v>13</v>
+      </c>
+      <c r="G38" t="str">
+        <f>VLOOKUP(F38,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39" t="str">
+        <f>VLOOKUP(B39,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39" t="str">
+        <f>VLOOKUP(F39,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>9</v>
+      </c>
+      <c r="C40" t="str">
+        <f>VLOOKUP(B40,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F40">
+        <v>6</v>
+      </c>
+      <c r="G40" t="str">
+        <f>VLOOKUP(F40,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>12</v>
+      </c>
+      <c r="C41" t="str">
+        <f>VLOOKUP(B41,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="str">
+        <f>VLOOKUP(F41,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>11</v>
+      </c>
+      <c r="C42" t="str">
+        <f>VLOOKUP(B42,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F42">
+        <v>4</v>
+      </c>
+      <c r="G42" t="str">
+        <f>VLOOKUP(F42,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43" t="str">
+        <f>VLOOKUP(B43,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43" t="str">
+        <f>VLOOKUP(F43,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>5</v>
+      </c>
+      <c r="C44" t="str">
+        <f>VLOOKUP(B44,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F44">
+        <v>13</v>
+      </c>
+      <c r="G44" t="str">
+        <f>VLOOKUP(F44,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" t="str">
+        <f>VLOOKUP(B45,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F45">
+        <v>7</v>
+      </c>
+      <c r="G45" t="str">
+        <f>VLOOKUP(F45,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>8</v>
+      </c>
+      <c r="C46" t="str">
+        <f>VLOOKUP(B46,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F46">
+        <v>9</v>
+      </c>
+      <c r="G46" t="str">
+        <f>VLOOKUP(F46,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47" t="str">
+        <f>VLOOKUP(B47,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+      <c r="G47" t="str">
+        <f>VLOOKUP(F47,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>3</v>
+      </c>
+      <c r="C48" t="str">
+        <f>VLOOKUP(B48,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F48">
+        <v>6</v>
+      </c>
+      <c r="G48" t="str">
+        <f>VLOOKUP(F48,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>4</v>
+      </c>
+      <c r="C49" t="str">
+        <f>VLOOKUP(B49,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F49">
+        <v>12</v>
+      </c>
+      <c r="G49" t="str">
+        <f>VLOOKUP(F49,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="str">
+        <f>VLOOKUP(B50,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F50">
+        <v>11</v>
+      </c>
+      <c r="G50" t="str">
+        <f>VLOOKUP(F50,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51" t="str">
+        <f>VLOOKUP(B51,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F51">
+        <v>7</v>
+      </c>
+      <c r="G51" t="str">
+        <f>VLOOKUP(F51,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>14</v>
+      </c>
+      <c r="C52" t="str">
+        <f>VLOOKUP(B52,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F52">
+        <v>11</v>
+      </c>
+      <c r="G52" t="str">
+        <f>VLOOKUP(F52,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>8</v>
+      </c>
+      <c r="C53" t="str">
+        <f>VLOOKUP(B53,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F53">
+        <v>3</v>
+      </c>
+      <c r="G53" t="str">
+        <f>VLOOKUP(F53,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>9</v>
+      </c>
+      <c r="C54" t="str">
+        <f>VLOOKUP(B54,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F54">
+        <v>10</v>
+      </c>
+      <c r="G54" t="str">
+        <f>VLOOKUP(F54,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55" t="str">
+        <f>VLOOKUP(B55,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+      <c r="G55" t="str">
+        <f>VLOOKUP(F55,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="str">
+        <f>VLOOKUP(B56,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F56">
+        <v>12</v>
+      </c>
+      <c r="G56" t="str">
+        <f>VLOOKUP(F56,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>6</v>
+      </c>
+      <c r="C57" t="str">
+        <f>VLOOKUP(B57,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F57">
+        <v>13</v>
+      </c>
+      <c r="G57" t="str">
+        <f>VLOOKUP(F57,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>5</v>
+      </c>
+      <c r="C58" t="str">
+        <f>VLOOKUP(B58,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F58">
+        <v>11</v>
+      </c>
+      <c r="G58" t="str">
+        <f>VLOOKUP(F58,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>14</v>
+      </c>
+      <c r="C59" t="str">
+        <f>VLOOKUP(B59,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F59">
+        <v>12</v>
+      </c>
+      <c r="G59" t="str">
+        <f>VLOOKUP(F59,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60" t="str">
+        <f>VLOOKUP(B60,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F60">
+        <v>13</v>
+      </c>
+      <c r="G60" t="str">
+        <f>VLOOKUP(F60,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>9</v>
+      </c>
+      <c r="C61" t="str">
+        <f>VLOOKUP(B61,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61" t="str">
+        <f>VLOOKUP(F61,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="str">
+        <f>VLOOKUP(B62,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="G62" t="str">
+        <f>VLOOKUP(F62,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63" t="str">
+        <f>VLOOKUP(B63,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F63">
+        <v>10</v>
+      </c>
+      <c r="G63" t="str">
+        <f>VLOOKUP(F63,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>7</v>
+      </c>
+      <c r="C64" t="str">
+        <f>VLOOKUP(B64,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F64">
+        <v>6</v>
+      </c>
+      <c r="G64" t="str">
+        <f>VLOOKUP(F64,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+      <c r="C65" t="str">
+        <f>VLOOKUP(B65,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F65">
+        <v>12</v>
+      </c>
+      <c r="G65" t="str">
+        <f>VLOOKUP(F65,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>14</v>
+      </c>
+      <c r="C66" t="str">
+        <f>VLOOKUP(B66,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66" t="str">
+        <f>VLOOKUP(F66,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>8</v>
+      </c>
+      <c r="C67" t="str">
+        <f>VLOOKUP(B67,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F67">
+        <v>7</v>
+      </c>
+      <c r="G67" t="str">
+        <f>VLOOKUP(F67,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>9</v>
+      </c>
+      <c r="C68" t="str">
+        <f>VLOOKUP(B68,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F68">
+        <v>13</v>
+      </c>
+      <c r="G68" t="str">
+        <f>VLOOKUP(F68,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>3</v>
+      </c>
+      <c r="C69" t="str">
+        <f>VLOOKUP(B69,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F69">
+        <v>10</v>
+      </c>
+      <c r="G69" t="str">
+        <f>VLOOKUP(F69,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>4</v>
+      </c>
+      <c r="C70" t="str">
+        <f>VLOOKUP(B70,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70" t="str">
+        <f>VLOOKUP(F70,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>6</v>
+      </c>
+      <c r="C71" t="str">
+        <f>VLOOKUP(B71,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F71">
+        <v>11</v>
+      </c>
+      <c r="G71" t="str">
+        <f>VLOOKUP(F71,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>5</v>
+      </c>
+      <c r="C72" t="str">
+        <f>VLOOKUP(B72,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72" t="str">
+        <f>VLOOKUP(F72,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>14</v>
+      </c>
+      <c r="C73" t="str">
+        <f>VLOOKUP(B73,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F73">
+        <v>4</v>
+      </c>
+      <c r="G73" t="str">
+        <f>VLOOKUP(F73,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>8</v>
+      </c>
+      <c r="C74" t="str">
+        <f>VLOOKUP(B74,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F74">
+        <v>11</v>
+      </c>
+      <c r="G74" t="str">
+        <f>VLOOKUP(F74,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>9</v>
+      </c>
+      <c r="C75" t="str">
+        <f>VLOOKUP(B75,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F75">
+        <v>7</v>
+      </c>
+      <c r="G75" t="str">
+        <f>VLOOKUP(F75,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>3</v>
+      </c>
+      <c r="C76" t="str">
+        <f>VLOOKUP(B76,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F76">
+        <v>13</v>
+      </c>
+      <c r="G76" t="str">
+        <f>VLOOKUP(F76,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>6</v>
+      </c>
+      <c r="C77" t="str">
+        <f>VLOOKUP(B77,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F77">
+        <v>12</v>
+      </c>
+      <c r="G77" t="str">
+        <f>VLOOKUP(F77,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>10</v>
+      </c>
+      <c r="C78" t="str">
+        <f>VLOOKUP(B78,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78" t="str">
+        <f>VLOOKUP(F78,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>5</v>
+      </c>
+      <c r="C79" t="str">
+        <f>VLOOKUP(B79,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F79">
+        <v>4</v>
+      </c>
+      <c r="G79" t="str">
+        <f>VLOOKUP(F79,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>14</v>
+      </c>
+      <c r="C80" t="str">
+        <f>VLOOKUP(B80,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80" t="str">
+        <f>VLOOKUP(F80,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>8</v>
+      </c>
+      <c r="C81" t="str">
+        <f>VLOOKUP(B81,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F81">
+        <v>12</v>
+      </c>
+      <c r="G81" t="str">
+        <f>VLOOKUP(F81,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>9</v>
+      </c>
+      <c r="C82" t="str">
+        <f>VLOOKUP(B82,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F82">
+        <v>11</v>
+      </c>
+      <c r="G82" t="str">
+        <f>VLOOKUP(F82,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>6</v>
+      </c>
+      <c r="C83" t="str">
+        <f>VLOOKUP(B83,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83" t="str">
+        <f>VLOOKUP(F83,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>13</v>
+      </c>
+      <c r="C84" t="str">
+        <f>VLOOKUP(B84,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84" t="str">
+        <f>VLOOKUP(F84,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>7</v>
+      </c>
+      <c r="C85" t="str">
+        <f>VLOOKUP(B85,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="G85" t="str">
+        <f>VLOOKUP(F85,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>5</v>
+      </c>
+      <c r="C86" t="str">
+        <f>VLOOKUP(B86,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+      <c r="G86" t="str">
+        <f>VLOOKUP(F86,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>14</v>
+      </c>
+      <c r="C87" t="str">
+        <f>VLOOKUP(B87,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F87">
+        <v>10</v>
+      </c>
+      <c r="G87" t="str">
+        <f>VLOOKUP(F87,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>8</v>
+      </c>
+      <c r="C88" t="str">
+        <f>VLOOKUP(B88,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88" t="str">
+        <f>VLOOKUP(F88,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>9</v>
+      </c>
+      <c r="C89" t="str">
+        <f>VLOOKUP(B89,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F89">
+        <v>12</v>
+      </c>
+      <c r="G89" t="str">
+        <f>VLOOKUP(F89,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>3</v>
+      </c>
+      <c r="C90" t="str">
+        <f>VLOOKUP(B90,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F90">
+        <v>11</v>
+      </c>
+      <c r="G90" t="str">
+        <f>VLOOKUP(F90,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>13</v>
+      </c>
+      <c r="C91" t="str">
+        <f>VLOOKUP(B91,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F91">
+        <v>7</v>
+      </c>
+      <c r="G91" t="str">
+        <f>VLOOKUP(F91,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>6</v>
+      </c>
+      <c r="C92" t="str">
+        <f>VLOOKUP(B92,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F92">
+        <v>4</v>
+      </c>
+      <c r="G92" t="str">
+        <f>VLOOKUP(F92,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>14</v>
+      </c>
+      <c r="C93" t="str">
+        <f>VLOOKUP(B93,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F93">
+        <v>5</v>
+      </c>
+      <c r="G93" t="str">
+        <f>VLOOKUP(F93,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>6</v>
+      </c>
+      <c r="C94" t="str">
+        <f>VLOOKUP(B94,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F94">
+        <v>1</v>
+      </c>
+      <c r="G94" t="str">
+        <f>VLOOKUP(F94,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95" t="str">
+        <f>VLOOKUP(B95,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F95">
+        <v>4</v>
+      </c>
+      <c r="G95" t="str">
+        <f>VLOOKUP(F95,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H95">
+        <f t="shared" ref="H95:H158" si="2">H88+1</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>9</v>
+      </c>
+      <c r="C96" t="str">
+        <f>VLOOKUP(B96,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F96">
+        <v>2</v>
+      </c>
+      <c r="G96" t="str">
+        <f>VLOOKUP(F96,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>3</v>
+      </c>
+      <c r="C97" t="str">
+        <f>VLOOKUP(B97,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F97">
+        <v>12</v>
+      </c>
+      <c r="G97" t="str">
+        <f>VLOOKUP(F97,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>13</v>
+      </c>
+      <c r="C98" t="str">
+        <f>VLOOKUP(B98,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F98">
+        <v>11</v>
+      </c>
+      <c r="G98" t="str">
+        <f>VLOOKUP(F98,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>7</v>
+      </c>
+      <c r="C99" t="str">
+        <f>VLOOKUP(B99,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F99">
+        <v>10</v>
+      </c>
+      <c r="G99" t="str">
+        <f>VLOOKUP(F99,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H99">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>14</v>
+      </c>
+      <c r="C100" t="str">
+        <f>VLOOKUP(B100,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F100">
+        <v>6</v>
+      </c>
+      <c r="G100" t="str">
+        <f>VLOOKUP(F100,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H100">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>5</v>
+      </c>
+      <c r="C101" t="str">
+        <f>VLOOKUP(B101,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F101">
+        <v>10</v>
+      </c>
+      <c r="G101" t="str">
+        <f>VLOOKUP(F101,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H101">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>8</v>
+      </c>
+      <c r="C102" t="str">
+        <f>VLOOKUP(B102,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102" t="str">
+        <f>VLOOKUP(F102,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H102">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>9</v>
+      </c>
+      <c r="C103" t="str">
+        <f>VLOOKUP(B103,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F103">
+        <v>4</v>
+      </c>
+      <c r="G103" t="str">
+        <f>VLOOKUP(F103,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H103">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>3</v>
+      </c>
+      <c r="C104" t="str">
+        <f>VLOOKUP(B104,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="G104" t="str">
+        <f>VLOOKUP(F104,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>13</v>
+      </c>
+      <c r="C105" t="str">
+        <f>VLOOKUP(B105,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F105">
+        <v>12</v>
+      </c>
+      <c r="G105" t="str">
+        <f>VLOOKUP(F105,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H105">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>7</v>
+      </c>
+      <c r="C106" t="str">
+        <f>VLOOKUP(B106,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F106">
+        <v>11</v>
+      </c>
+      <c r="G106" t="str">
+        <f>VLOOKUP(F106,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>5</v>
+      </c>
+      <c r="C107" t="str">
+        <f>VLOOKUP(B107,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F107">
+        <v>6</v>
+      </c>
+      <c r="G107" t="str">
+        <f>VLOOKUP(F107,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H107">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>14</v>
+      </c>
+      <c r="C108" t="str">
+        <f>VLOOKUP(B108,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F108">
+        <v>8</v>
+      </c>
+      <c r="G108" t="str">
+        <f>VLOOKUP(F108,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="H108">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>3</v>
+      </c>
+      <c r="C109" t="str">
+        <f>VLOOKUP(B109,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F109">
+        <v>4</v>
+      </c>
+      <c r="G109" t="str">
+        <f>VLOOKUP(F109,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H109">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>9</v>
+      </c>
+      <c r="C110" t="str">
+        <f>VLOOKUP(B110,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F110">
+        <v>1</v>
+      </c>
+      <c r="G110" t="str">
+        <f>VLOOKUP(F110,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H110">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>11</v>
+      </c>
+      <c r="C111" t="str">
+        <f>VLOOKUP(B111,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F111">
+        <v>10</v>
+      </c>
+      <c r="G111" t="str">
+        <f>VLOOKUP(F111,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H111">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>13</v>
+      </c>
+      <c r="C112" t="str">
+        <f>VLOOKUP(B112,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F112">
+        <v>2</v>
+      </c>
+      <c r="G112" t="str">
+        <f>VLOOKUP(F112,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H112">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>7</v>
+      </c>
+      <c r="C113" t="str">
+        <f>VLOOKUP(B113,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F113">
+        <v>12</v>
+      </c>
+      <c r="G113" t="str">
+        <f>VLOOKUP(F113,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H113">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>5</v>
+      </c>
+      <c r="C114" t="str">
+        <f>VLOOKUP(B114,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F114">
+        <v>8</v>
+      </c>
+      <c r="G114" t="str">
+        <f>VLOOKUP(F114,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="H114">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>14</v>
+      </c>
+      <c r="C115" t="str">
+        <f>VLOOKUP(B115,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F115">
+        <v>9</v>
+      </c>
+      <c r="G115" t="str">
+        <f>VLOOKUP(F115,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="H115">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="C116" t="str">
+        <f>VLOOKUP(B116,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F116">
+        <v>1</v>
+      </c>
+      <c r="G116" t="str">
+        <f>VLOOKUP(F116,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H116">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>11</v>
+      </c>
+      <c r="C117" t="str">
+        <f>VLOOKUP(B117,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F117">
+        <v>12</v>
+      </c>
+      <c r="G117" t="str">
+        <f>VLOOKUP(F117,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H117">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>6</v>
+      </c>
+      <c r="C118" t="str">
+        <f>VLOOKUP(B118,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F118">
+        <v>10</v>
+      </c>
+      <c r="G118" t="str">
+        <f>VLOOKUP(F118,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H118">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>4</v>
+      </c>
+      <c r="C119" t="str">
+        <f>VLOOKUP(B119,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F119">
+        <v>13</v>
+      </c>
+      <c r="G119" t="str">
+        <f>VLOOKUP(F119,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H119">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>7</v>
+      </c>
+      <c r="C120" t="str">
+        <f>VLOOKUP(B120,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+      <c r="G120" t="str">
+        <f>VLOOKUP(F120,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H120">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>5</v>
+      </c>
+      <c r="C121" t="str">
+        <f>VLOOKUP(B121,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F121">
+        <v>9</v>
+      </c>
+      <c r="G121" t="str">
+        <f>VLOOKUP(F121,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="H121">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>14</v>
+      </c>
+      <c r="C122" t="str">
+        <f>VLOOKUP(B122,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F122">
+        <v>3</v>
+      </c>
+      <c r="G122" t="str">
+        <f>VLOOKUP(F122,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H122">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>8</v>
+      </c>
+      <c r="C123" t="str">
+        <f>VLOOKUP(B123,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F123">
+        <v>6</v>
+      </c>
+      <c r="G123" t="str">
+        <f>VLOOKUP(F123,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H123">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>7</v>
+      </c>
+      <c r="C124" t="str">
+        <f>VLOOKUP(B124,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F124">
+        <v>4</v>
+      </c>
+      <c r="G124" t="str">
+        <f>VLOOKUP(F124,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H124">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>11</v>
+      </c>
+      <c r="C125" t="str">
+        <f>VLOOKUP(B125,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F125">
+        <v>2</v>
+      </c>
+      <c r="G125" t="str">
+        <f>VLOOKUP(F125,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H125">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>13</v>
+      </c>
+      <c r="C126" t="str">
+        <f>VLOOKUP(B126,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126" t="str">
+        <f>VLOOKUP(F126,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H126">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>10</v>
+      </c>
+      <c r="C127" t="str">
+        <f>VLOOKUP(B127,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F127">
+        <v>12</v>
+      </c>
+      <c r="G127" t="str">
+        <f>VLOOKUP(F127,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H127">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>5</v>
+      </c>
+      <c r="C128" t="str">
+        <f>VLOOKUP(B128,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F128">
+        <v>3</v>
+      </c>
+      <c r="G128" t="str">
+        <f>VLOOKUP(F128,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H128">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>14</v>
+      </c>
+      <c r="C129" t="str">
+        <f>VLOOKUP(B129,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F129">
+        <v>13</v>
+      </c>
+      <c r="G129" t="str">
+        <f>VLOOKUP(F129,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H129">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>8</v>
+      </c>
+      <c r="C130" t="str">
+        <f>VLOOKUP(B130,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F130">
+        <v>10</v>
+      </c>
+      <c r="G130" t="str">
+        <f>VLOOKUP(F130,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H130">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>9</v>
+      </c>
+      <c r="C131" t="str">
+        <f>VLOOKUP(B131,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F131">
+        <v>6</v>
+      </c>
+      <c r="G131" t="str">
+        <f>VLOOKUP(F131,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H131">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>12</v>
+      </c>
+      <c r="C132" t="str">
+        <f>VLOOKUP(B132,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+      <c r="G132" t="str">
+        <f>VLOOKUP(F132,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H132">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>11</v>
+      </c>
+      <c r="C133" t="str">
+        <f>VLOOKUP(B133,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F133">
+        <v>4</v>
+      </c>
+      <c r="G133" t="str">
+        <f>VLOOKUP(F133,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H133">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7</v>
+      </c>
+      <c r="C134" t="str">
+        <f>VLOOKUP(B134,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" t="str">
+        <f>VLOOKUP(F134,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H134">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>5</v>
+      </c>
+      <c r="C135" t="str">
+        <f>VLOOKUP(B135,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F135">
+        <v>13</v>
+      </c>
+      <c r="G135" t="str">
+        <f>VLOOKUP(F135,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H135">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>14</v>
+      </c>
+      <c r="C136" t="str">
+        <f>VLOOKUP(B136,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F136">
+        <v>7</v>
+      </c>
+      <c r="G136" t="str">
+        <f>VLOOKUP(F136,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H136">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>8</v>
+      </c>
+      <c r="C137" t="str">
+        <f>VLOOKUP(B137,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F137">
+        <v>9</v>
+      </c>
+      <c r="G137" t="str">
+        <f>VLOOKUP(F137,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="H137">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>10</v>
+      </c>
+      <c r="C138" t="str">
+        <f>VLOOKUP(B138,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F138">
+        <v>2</v>
+      </c>
+      <c r="G138" t="str">
+        <f>VLOOKUP(F138,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H138">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>3</v>
+      </c>
+      <c r="C139" t="str">
+        <f>VLOOKUP(B139,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F139">
+        <v>6</v>
+      </c>
+      <c r="G139" t="str">
+        <f>VLOOKUP(F139,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H139">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>4</v>
+      </c>
+      <c r="C140" t="str">
+        <f>VLOOKUP(B140,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F140">
+        <v>12</v>
+      </c>
+      <c r="G140" t="str">
+        <f>VLOOKUP(F140,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H140">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141" t="str">
+        <f>VLOOKUP(B141,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F141">
+        <v>11</v>
+      </c>
+      <c r="G141" t="str">
+        <f>VLOOKUP(F141,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H141">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>5</v>
+      </c>
+      <c r="C142" t="str">
+        <f>VLOOKUP(B142,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F142">
+        <v>7</v>
+      </c>
+      <c r="G142" t="str">
+        <f>VLOOKUP(F142,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H142">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>14</v>
+      </c>
+      <c r="C143" t="str">
+        <f>VLOOKUP(B143,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F143">
+        <v>11</v>
+      </c>
+      <c r="G143" t="str">
+        <f>VLOOKUP(F143,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H143">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>8</v>
+      </c>
+      <c r="C144" t="str">
+        <f>VLOOKUP(B144,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F144">
+        <v>3</v>
+      </c>
+      <c r="G144" t="str">
+        <f>VLOOKUP(F144,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H144">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>9</v>
+      </c>
+      <c r="C145" t="str">
+        <f>VLOOKUP(B145,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F145">
+        <v>10</v>
+      </c>
+      <c r="G145" t="str">
+        <f>VLOOKUP(F145,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H145">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>4</v>
+      </c>
+      <c r="C146" t="str">
+        <f>VLOOKUP(B146,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F146">
+        <v>2</v>
+      </c>
+      <c r="G146" t="str">
+        <f>VLOOKUP(F146,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H146">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147" t="str">
+        <f>VLOOKUP(B147,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F147">
+        <v>12</v>
+      </c>
+      <c r="G147" t="str">
+        <f>VLOOKUP(F147,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H147">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>6</v>
+      </c>
+      <c r="C148" t="str">
+        <f>VLOOKUP(B148,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F148">
+        <v>13</v>
+      </c>
+      <c r="G148" t="str">
+        <f>VLOOKUP(F148,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H148">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>5</v>
+      </c>
+      <c r="C149" t="str">
+        <f>VLOOKUP(B149,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F149">
+        <v>11</v>
+      </c>
+      <c r="G149" t="str">
+        <f>VLOOKUP(F149,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H149">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>14</v>
+      </c>
+      <c r="C150" t="str">
+        <f>VLOOKUP(B150,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F150">
+        <v>12</v>
+      </c>
+      <c r="G150" t="str">
+        <f>VLOOKUP(F150,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H150">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>8</v>
+      </c>
+      <c r="C151" t="str">
+        <f>VLOOKUP(B151,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F151">
+        <v>13</v>
+      </c>
+      <c r="G151" t="str">
+        <f>VLOOKUP(F151,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H151">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>9</v>
+      </c>
+      <c r="C152" t="str">
+        <f>VLOOKUP(B152,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F152">
+        <v>3</v>
+      </c>
+      <c r="G152" t="str">
+        <f>VLOOKUP(F152,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H152">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153" t="str">
+        <f>VLOOKUP(B153,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F153">
+        <v>2</v>
+      </c>
+      <c r="G153" t="str">
+        <f>VLOOKUP(F153,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H153">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>4</v>
+      </c>
+      <c r="C154" t="str">
+        <f>VLOOKUP(B154,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F154">
+        <v>10</v>
+      </c>
+      <c r="G154" t="str">
+        <f>VLOOKUP(F154,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H154">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7</v>
+      </c>
+      <c r="C155" t="str">
+        <f>VLOOKUP(B155,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F155">
+        <v>6</v>
+      </c>
+      <c r="G155" t="str">
+        <f>VLOOKUP(F155,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H155">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>5</v>
+      </c>
+      <c r="C156" t="str">
+        <f>VLOOKUP(B156,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F156">
+        <v>12</v>
+      </c>
+      <c r="G156" t="str">
+        <f>VLOOKUP(F156,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H156">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>14</v>
+      </c>
+      <c r="C157" t="str">
+        <f>VLOOKUP(B157,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F157">
+        <v>2</v>
+      </c>
+      <c r="G157" t="str">
+        <f>VLOOKUP(F157,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H157">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>8</v>
+      </c>
+      <c r="C158" t="str">
+        <f>VLOOKUP(B158,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F158">
+        <v>7</v>
+      </c>
+      <c r="G158" t="str">
+        <f>VLOOKUP(F158,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H158">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>9</v>
+      </c>
+      <c r="C159" t="str">
+        <f>VLOOKUP(B159,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F159">
+        <v>13</v>
+      </c>
+      <c r="G159" t="str">
+        <f>VLOOKUP(F159,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H159">
+        <f t="shared" ref="H159:H222" si="3">H152+1</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>3</v>
+      </c>
+      <c r="C160" t="str">
+        <f>VLOOKUP(B160,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F160">
+        <v>10</v>
+      </c>
+      <c r="G160" t="str">
+        <f>VLOOKUP(F160,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H160">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161" t="str">
+        <f>VLOOKUP(B161,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161" t="str">
+        <f>VLOOKUP(F161,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H161">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>6</v>
+      </c>
+      <c r="C162" t="str">
+        <f>VLOOKUP(B162,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F162">
+        <v>11</v>
+      </c>
+      <c r="G162" t="str">
+        <f>VLOOKUP(F162,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H162">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>5</v>
+      </c>
+      <c r="C163" t="str">
+        <f>VLOOKUP(B163,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F163">
+        <v>2</v>
+      </c>
+      <c r="G163" t="str">
+        <f>VLOOKUP(F163,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H163">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>14</v>
+      </c>
+      <c r="C164" t="str">
+        <f>VLOOKUP(B164,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F164">
+        <v>4</v>
+      </c>
+      <c r="G164" t="str">
+        <f>VLOOKUP(F164,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H164">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>8</v>
+      </c>
+      <c r="C165" t="str">
+        <f>VLOOKUP(B165,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F165">
+        <v>11</v>
+      </c>
+      <c r="G165" t="str">
+        <f>VLOOKUP(F165,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H165">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>9</v>
+      </c>
+      <c r="C166" t="str">
+        <f>VLOOKUP(B166,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F166">
+        <v>7</v>
+      </c>
+      <c r="G166" t="str">
+        <f>VLOOKUP(F166,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H166">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>3</v>
+      </c>
+      <c r="C167" t="str">
+        <f>VLOOKUP(B167,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F167">
+        <v>13</v>
+      </c>
+      <c r="G167" t="str">
+        <f>VLOOKUP(F167,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H167">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>6</v>
+      </c>
+      <c r="C168" t="str">
+        <f>VLOOKUP(B168,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F168">
+        <v>12</v>
+      </c>
+      <c r="G168" t="str">
+        <f>VLOOKUP(F168,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H168">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>10</v>
+      </c>
+      <c r="C169" t="str">
+        <f>VLOOKUP(B169,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F169">
+        <v>1</v>
+      </c>
+      <c r="G169" t="str">
+        <f>VLOOKUP(F169,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H169">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>5</v>
+      </c>
+      <c r="C170" t="str">
+        <f>VLOOKUP(B170,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F170">
+        <v>4</v>
+      </c>
+      <c r="G170" t="str">
+        <f>VLOOKUP(F170,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H170">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>14</v>
+      </c>
+      <c r="C171" t="str">
+        <f>VLOOKUP(B171,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171" t="str">
+        <f>VLOOKUP(F171,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H171">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>8</v>
+      </c>
+      <c r="C172" t="str">
+        <f>VLOOKUP(B172,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F172">
+        <v>12</v>
+      </c>
+      <c r="G172" t="str">
+        <f>VLOOKUP(F172,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H172">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>9</v>
+      </c>
+      <c r="C173" t="str">
+        <f>VLOOKUP(B173,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F173">
+        <v>11</v>
+      </c>
+      <c r="G173" t="str">
+        <f>VLOOKUP(F173,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H173">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>6</v>
+      </c>
+      <c r="C174" t="str">
+        <f>VLOOKUP(B174,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F174">
+        <v>2</v>
+      </c>
+      <c r="G174" t="str">
+        <f>VLOOKUP(F174,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H174">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>13</v>
+      </c>
+      <c r="C175" t="str">
+        <f>VLOOKUP(B175,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F175">
+        <v>10</v>
+      </c>
+      <c r="G175" t="str">
+        <f>VLOOKUP(F175,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H175">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7</v>
+      </c>
+      <c r="C176" t="str">
+        <f>VLOOKUP(B176,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F176">
+        <v>3</v>
+      </c>
+      <c r="G176" t="str">
+        <f>VLOOKUP(F176,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H176">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>5</v>
+      </c>
+      <c r="C177" t="str">
+        <f>VLOOKUP(B177,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F177">
+        <v>1</v>
+      </c>
+      <c r="G177" t="str">
+        <f>VLOOKUP(F177,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H177">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>14</v>
+      </c>
+      <c r="C178" t="str">
+        <f>VLOOKUP(B178,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F178">
+        <v>10</v>
+      </c>
+      <c r="G178" t="str">
+        <f>VLOOKUP(F178,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H178">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>8</v>
+      </c>
+      <c r="C179" t="str">
+        <f>VLOOKUP(B179,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F179">
+        <v>2</v>
+      </c>
+      <c r="G179" t="str">
+        <f>VLOOKUP(F179,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H179">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>9</v>
+      </c>
+      <c r="C180" t="str">
+        <f>VLOOKUP(B180,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F180">
+        <v>12</v>
+      </c>
+      <c r="G180" t="str">
+        <f>VLOOKUP(F180,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H180">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>3</v>
+      </c>
+      <c r="C181" t="str">
+        <f>VLOOKUP(B181,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F181">
+        <v>11</v>
+      </c>
+      <c r="G181" t="str">
+        <f>VLOOKUP(F181,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H181">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>13</v>
+      </c>
+      <c r="C182" t="str">
+        <f>VLOOKUP(B182,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F182">
+        <v>7</v>
+      </c>
+      <c r="G182" t="str">
+        <f>VLOOKUP(F182,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H182">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>6</v>
+      </c>
+      <c r="C183" t="str">
+        <f>VLOOKUP(B183,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F183">
+        <v>4</v>
+      </c>
+      <c r="G183" t="str">
+        <f>VLOOKUP(F183,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H183">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>14</v>
+      </c>
+      <c r="C184" t="str">
+        <f>VLOOKUP(B184,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F184">
+        <v>5</v>
+      </c>
+      <c r="G184" t="str">
+        <f>VLOOKUP(F184,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="H184">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>6</v>
+      </c>
+      <c r="C185" t="str">
+        <f>VLOOKUP(B185,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185" t="str">
+        <f>VLOOKUP(F185,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H185">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>8</v>
+      </c>
+      <c r="C186" t="str">
+        <f>VLOOKUP(B186,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F186">
+        <v>4</v>
+      </c>
+      <c r="G186" t="str">
+        <f>VLOOKUP(F186,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H186">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>9</v>
+      </c>
+      <c r="C187" t="str">
+        <f>VLOOKUP(B187,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F187">
+        <v>2</v>
+      </c>
+      <c r="G187" t="str">
+        <f>VLOOKUP(F187,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H187">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>3</v>
+      </c>
+      <c r="C188" t="str">
+        <f>VLOOKUP(B188,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F188">
+        <v>12</v>
+      </c>
+      <c r="G188" t="str">
+        <f>VLOOKUP(F188,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H188">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>13</v>
+      </c>
+      <c r="C189" t="str">
+        <f>VLOOKUP(B189,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F189">
+        <v>11</v>
+      </c>
+      <c r="G189" t="str">
+        <f>VLOOKUP(F189,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H189">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7</v>
+      </c>
+      <c r="C190" t="str">
+        <f>VLOOKUP(B190,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F190">
+        <v>10</v>
+      </c>
+      <c r="G190" t="str">
+        <f>VLOOKUP(F190,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H190">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>14</v>
+      </c>
+      <c r="C191" t="str">
+        <f>VLOOKUP(B191,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F191">
+        <v>6</v>
+      </c>
+      <c r="G191" t="str">
+        <f>VLOOKUP(F191,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H191">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>5</v>
+      </c>
+      <c r="C192" t="str">
+        <f>VLOOKUP(B192,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F192">
+        <v>10</v>
+      </c>
+      <c r="G192" t="str">
+        <f>VLOOKUP(F192,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H192">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>8</v>
+      </c>
+      <c r="C193" t="str">
+        <f>VLOOKUP(B193,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F193">
+        <v>1</v>
+      </c>
+      <c r="G193" t="str">
+        <f>VLOOKUP(F193,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H193">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>9</v>
+      </c>
+      <c r="C194" t="str">
+        <f>VLOOKUP(B194,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F194">
+        <v>4</v>
+      </c>
+      <c r="G194" t="str">
+        <f>VLOOKUP(F194,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H194">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>3</v>
+      </c>
+      <c r="C195" t="str">
+        <f>VLOOKUP(B195,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+      <c r="G195" t="str">
+        <f>VLOOKUP(F195,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H195">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>13</v>
+      </c>
+      <c r="C196" t="str">
+        <f>VLOOKUP(B196,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F196">
+        <v>12</v>
+      </c>
+      <c r="G196" t="str">
+        <f>VLOOKUP(F196,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H196">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7</v>
+      </c>
+      <c r="C197" t="str">
+        <f>VLOOKUP(B197,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F197">
+        <v>11</v>
+      </c>
+      <c r="G197" t="str">
+        <f>VLOOKUP(F197,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H197">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>5</v>
+      </c>
+      <c r="C198" t="str">
+        <f>VLOOKUP(B198,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F198">
+        <v>6</v>
+      </c>
+      <c r="G198" t="str">
+        <f>VLOOKUP(F198,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H198">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>14</v>
+      </c>
+      <c r="C199" t="str">
+        <f>VLOOKUP(B199,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F199">
+        <v>8</v>
+      </c>
+      <c r="G199" t="str">
+        <f>VLOOKUP(F199,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="H199">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>3</v>
+      </c>
+      <c r="C200" t="str">
+        <f>VLOOKUP(B200,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F200">
+        <v>4</v>
+      </c>
+      <c r="G200" t="str">
+        <f>VLOOKUP(F200,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H200">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>9</v>
+      </c>
+      <c r="C201" t="str">
+        <f>VLOOKUP(B201,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F201">
+        <v>1</v>
+      </c>
+      <c r="G201" t="str">
+        <f>VLOOKUP(F201,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H201">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>11</v>
+      </c>
+      <c r="C202" t="str">
+        <f>VLOOKUP(B202,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F202">
+        <v>10</v>
+      </c>
+      <c r="G202" t="str">
+        <f>VLOOKUP(F202,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H202">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>13</v>
+      </c>
+      <c r="C203" t="str">
+        <f>VLOOKUP(B203,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F203">
+        <v>2</v>
+      </c>
+      <c r="G203" t="str">
+        <f>VLOOKUP(F203,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H203">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7</v>
+      </c>
+      <c r="C204" t="str">
+        <f>VLOOKUP(B204,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F204">
+        <v>12</v>
+      </c>
+      <c r="G204" t="str">
+        <f>VLOOKUP(F204,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H204">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>5</v>
+      </c>
+      <c r="C205" t="str">
+        <f>VLOOKUP(B205,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F205">
+        <v>8</v>
+      </c>
+      <c r="G205" t="str">
+        <f>VLOOKUP(F205,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="H205">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>14</v>
+      </c>
+      <c r="C206" t="str">
+        <f>VLOOKUP(B206,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F206">
+        <v>9</v>
+      </c>
+      <c r="G206" t="str">
+        <f>VLOOKUP(F206,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="H206">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>3</v>
+      </c>
+      <c r="C207" t="str">
+        <f>VLOOKUP(B207,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207" t="str">
+        <f>VLOOKUP(F207,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H207">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>11</v>
+      </c>
+      <c r="C208" t="str">
+        <f>VLOOKUP(B208,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F208">
+        <v>12</v>
+      </c>
+      <c r="G208" t="str">
+        <f>VLOOKUP(F208,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H208">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>6</v>
+      </c>
+      <c r="C209" t="str">
+        <f>VLOOKUP(B209,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F209">
+        <v>10</v>
+      </c>
+      <c r="G209" t="str">
+        <f>VLOOKUP(F209,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H209">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>4</v>
+      </c>
+      <c r="C210" t="str">
+        <f>VLOOKUP(B210,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F210">
+        <v>13</v>
+      </c>
+      <c r="G210" t="str">
+        <f>VLOOKUP(F210,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H210">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7</v>
+      </c>
+      <c r="C211" t="str">
+        <f>VLOOKUP(B211,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F211">
+        <v>2</v>
+      </c>
+      <c r="G211" t="str">
+        <f>VLOOKUP(F211,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H211">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>5</v>
+      </c>
+      <c r="C212" t="str">
+        <f>VLOOKUP(B212,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F212">
+        <v>9</v>
+      </c>
+      <c r="G212" t="str">
+        <f>VLOOKUP(F212,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="H212">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>14</v>
+      </c>
+      <c r="C213" t="str">
+        <f>VLOOKUP(B213,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F213">
+        <v>3</v>
+      </c>
+      <c r="G213" t="str">
+        <f>VLOOKUP(F213,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H213">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>8</v>
+      </c>
+      <c r="C214" t="str">
+        <f>VLOOKUP(B214,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F214">
+        <v>6</v>
+      </c>
+      <c r="G214" t="str">
+        <f>VLOOKUP(F214,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H214">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7</v>
+      </c>
+      <c r="C215" t="str">
+        <f>VLOOKUP(B215,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F215">
+        <v>4</v>
+      </c>
+      <c r="G215" t="str">
+        <f>VLOOKUP(F215,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H215">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>11</v>
+      </c>
+      <c r="C216" t="str">
+        <f>VLOOKUP(B216,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F216">
+        <v>2</v>
+      </c>
+      <c r="G216" t="str">
+        <f>VLOOKUP(F216,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H216">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>13</v>
+      </c>
+      <c r="C217" t="str">
+        <f>VLOOKUP(B217,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217" t="str">
+        <f>VLOOKUP(F217,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H217">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>10</v>
+      </c>
+      <c r="C218" t="str">
+        <f>VLOOKUP(B218,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F218">
+        <v>12</v>
+      </c>
+      <c r="G218" t="str">
+        <f>VLOOKUP(F218,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H218">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>5</v>
+      </c>
+      <c r="C219" t="str">
+        <f>VLOOKUP(B219,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F219">
+        <v>3</v>
+      </c>
+      <c r="G219" t="str">
+        <f>VLOOKUP(F219,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H219">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>14</v>
+      </c>
+      <c r="C220" t="str">
+        <f>VLOOKUP(B220,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F220">
+        <v>13</v>
+      </c>
+      <c r="G220" t="str">
+        <f>VLOOKUP(F220,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H220">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>8</v>
+      </c>
+      <c r="C221" t="str">
+        <f>VLOOKUP(B221,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F221">
+        <v>10</v>
+      </c>
+      <c r="G221" t="str">
+        <f>VLOOKUP(F221,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H221">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>9</v>
+      </c>
+      <c r="C222" t="str">
+        <f>VLOOKUP(B222,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F222">
+        <v>6</v>
+      </c>
+      <c r="G222" t="str">
+        <f>VLOOKUP(F222,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H222">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>12</v>
+      </c>
+      <c r="C223" t="str">
+        <f>VLOOKUP(B223,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="F223">
+        <v>2</v>
+      </c>
+      <c r="G223" t="str">
+        <f>VLOOKUP(F223,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H223">
+        <f t="shared" ref="H223:H274" si="4">H216+1</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>11</v>
+      </c>
+      <c r="C224" t="str">
+        <f>VLOOKUP(B224,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="F224">
+        <v>4</v>
+      </c>
+      <c r="G224" t="str">
+        <f>VLOOKUP(F224,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H224">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7</v>
+      </c>
+      <c r="C225" t="str">
+        <f>VLOOKUP(B225,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+      <c r="G225" t="str">
+        <f>VLOOKUP(F225,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H225">
+        <f t="shared" si="4"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>5</v>
+      </c>
+      <c r="C226" t="str">
+        <f>VLOOKUP(B226,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F226">
+        <v>13</v>
+      </c>
+      <c r="G226" t="str">
+        <f>VLOOKUP(F226,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H226">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>14</v>
+      </c>
+      <c r="C227" t="str">
+        <f>VLOOKUP(B227,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F227">
+        <v>7</v>
+      </c>
+      <c r="G227" t="str">
+        <f>VLOOKUP(F227,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H227">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>8</v>
+      </c>
+      <c r="C228" t="str">
+        <f>VLOOKUP(B228,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F228">
+        <v>9</v>
+      </c>
+      <c r="G228" t="str">
+        <f>VLOOKUP(F228,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="H228">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>10</v>
+      </c>
+      <c r="C229" t="str">
+        <f>VLOOKUP(B229,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F229">
+        <v>2</v>
+      </c>
+      <c r="G229" t="str">
+        <f>VLOOKUP(F229,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H229">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>3</v>
+      </c>
+      <c r="C230" t="str">
+        <f>VLOOKUP(B230,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F230">
+        <v>6</v>
+      </c>
+      <c r="G230" t="str">
+        <f>VLOOKUP(F230,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H230">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>4</v>
+      </c>
+      <c r="C231" t="str">
+        <f>VLOOKUP(B231,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F231">
+        <v>12</v>
+      </c>
+      <c r="G231" t="str">
+        <f>VLOOKUP(F231,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H231">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+      <c r="C232" t="str">
+        <f>VLOOKUP(B232,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F232">
+        <v>11</v>
+      </c>
+      <c r="G232" t="str">
+        <f>VLOOKUP(F232,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H232">
+        <f t="shared" si="4"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>5</v>
+      </c>
+      <c r="C233" t="str">
+        <f>VLOOKUP(B233,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F233">
+        <v>7</v>
+      </c>
+      <c r="G233" t="str">
+        <f>VLOOKUP(F233,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H233">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>14</v>
+      </c>
+      <c r="C234" t="str">
+        <f>VLOOKUP(B234,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F234">
+        <v>11</v>
+      </c>
+      <c r="G234" t="str">
+        <f>VLOOKUP(F234,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H234">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>8</v>
+      </c>
+      <c r="C235" t="str">
+        <f>VLOOKUP(B235,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F235">
+        <v>3</v>
+      </c>
+      <c r="G235" t="str">
+        <f>VLOOKUP(F235,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H235">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>9</v>
+      </c>
+      <c r="C236" t="str">
+        <f>VLOOKUP(B236,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F236">
+        <v>10</v>
+      </c>
+      <c r="G236" t="str">
+        <f>VLOOKUP(F236,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H236">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>4</v>
+      </c>
+      <c r="C237" t="str">
+        <f>VLOOKUP(B237,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F237">
+        <v>2</v>
+      </c>
+      <c r="G237" t="str">
+        <f>VLOOKUP(F237,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H237">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>1</v>
+      </c>
+      <c r="C238" t="str">
+        <f>VLOOKUP(B238,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F238">
+        <v>12</v>
+      </c>
+      <c r="G238" t="str">
+        <f>VLOOKUP(F238,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H238">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>6</v>
+      </c>
+      <c r="C239" t="str">
+        <f>VLOOKUP(B239,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F239">
+        <v>13</v>
+      </c>
+      <c r="G239" t="str">
+        <f>VLOOKUP(F239,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H239">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>5</v>
+      </c>
+      <c r="C240" t="str">
+        <f>VLOOKUP(B240,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F240">
+        <v>11</v>
+      </c>
+      <c r="G240" t="str">
+        <f>VLOOKUP(F240,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H240">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>14</v>
+      </c>
+      <c r="C241" t="str">
+        <f>VLOOKUP(B241,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F241">
+        <v>12</v>
+      </c>
+      <c r="G241" t="str">
+        <f>VLOOKUP(F241,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H241">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>8</v>
+      </c>
+      <c r="C242" t="str">
+        <f>VLOOKUP(B242,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F242">
+        <v>13</v>
+      </c>
+      <c r="G242" t="str">
+        <f>VLOOKUP(F242,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H242">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>9</v>
+      </c>
+      <c r="C243" t="str">
+        <f>VLOOKUP(B243,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F243">
+        <v>3</v>
+      </c>
+      <c r="G243" t="str">
+        <f>VLOOKUP(F243,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H243">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>1</v>
+      </c>
+      <c r="C244" t="str">
+        <f>VLOOKUP(B244,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="F244">
+        <v>2</v>
+      </c>
+      <c r="G244" t="str">
+        <f>VLOOKUP(F244,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H244">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>4</v>
+      </c>
+      <c r="C245" t="str">
+        <f>VLOOKUP(B245,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F245">
+        <v>10</v>
+      </c>
+      <c r="G245" t="str">
+        <f>VLOOKUP(F245,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H245">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7</v>
+      </c>
+      <c r="C246" t="str">
+        <f>VLOOKUP(B246,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F246">
+        <v>6</v>
+      </c>
+      <c r="G246" t="str">
+        <f>VLOOKUP(F246,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="H246">
+        <f t="shared" si="4"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>5</v>
+      </c>
+      <c r="C247" t="str">
+        <f>VLOOKUP(B247,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F247">
+        <v>12</v>
+      </c>
+      <c r="G247" t="str">
+        <f>VLOOKUP(F247,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H247">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>14</v>
+      </c>
+      <c r="C248" t="str">
+        <f>VLOOKUP(B248,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F248">
+        <v>2</v>
+      </c>
+      <c r="G248" t="str">
+        <f>VLOOKUP(F248,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H248">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>8</v>
+      </c>
+      <c r="C249" t="str">
+        <f>VLOOKUP(B249,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F249">
+        <v>7</v>
+      </c>
+      <c r="G249" t="str">
+        <f>VLOOKUP(F249,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H249">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>9</v>
+      </c>
+      <c r="C250" t="str">
+        <f>VLOOKUP(B250,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F250">
+        <v>13</v>
+      </c>
+      <c r="G250" t="str">
+        <f>VLOOKUP(F250,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H250">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>3</v>
+      </c>
+      <c r="C251" t="str">
+        <f>VLOOKUP(B251,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F251">
+        <v>10</v>
+      </c>
+      <c r="G251" t="str">
+        <f>VLOOKUP(F251,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H251">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>4</v>
+      </c>
+      <c r="C252" t="str">
+        <f>VLOOKUP(B252,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="F252">
+        <v>1</v>
+      </c>
+      <c r="G252" t="str">
+        <f>VLOOKUP(F252,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H252">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>6</v>
+      </c>
+      <c r="C253" t="str">
+        <f>VLOOKUP(B253,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F253">
+        <v>11</v>
+      </c>
+      <c r="G253" t="str">
+        <f>VLOOKUP(F253,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H253">
+        <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>5</v>
+      </c>
+      <c r="C254" t="str">
+        <f>VLOOKUP(B254,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F254">
+        <v>2</v>
+      </c>
+      <c r="G254" t="str">
+        <f>VLOOKUP(F254,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H254">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>14</v>
+      </c>
+      <c r="C255" t="str">
+        <f>VLOOKUP(B255,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F255">
+        <v>4</v>
+      </c>
+      <c r="G255" t="str">
+        <f>VLOOKUP(F255,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H255">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>8</v>
+      </c>
+      <c r="C256" t="str">
+        <f>VLOOKUP(B256,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F256">
+        <v>11</v>
+      </c>
+      <c r="G256" t="str">
+        <f>VLOOKUP(F256,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H256">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>9</v>
+      </c>
+      <c r="C257" t="str">
+        <f>VLOOKUP(B257,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F257">
+        <v>7</v>
+      </c>
+      <c r="G257" t="str">
+        <f>VLOOKUP(F257,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H257">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>3</v>
+      </c>
+      <c r="C258" t="str">
+        <f>VLOOKUP(B258,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F258">
+        <v>13</v>
+      </c>
+      <c r="G258" t="str">
+        <f>VLOOKUP(F258,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="H258">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>6</v>
+      </c>
+      <c r="C259" t="str">
+        <f>VLOOKUP(B259,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F259">
+        <v>12</v>
+      </c>
+      <c r="G259" t="str">
+        <f>VLOOKUP(F259,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H259">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>10</v>
+      </c>
+      <c r="C260" t="str">
+        <f>VLOOKUP(B260,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="F260">
+        <v>1</v>
+      </c>
+      <c r="G260" t="str">
+        <f>VLOOKUP(F260,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H260">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>5</v>
+      </c>
+      <c r="C261" t="str">
+        <f>VLOOKUP(B261,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F261">
+        <v>4</v>
+      </c>
+      <c r="G261" t="str">
+        <f>VLOOKUP(F261,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H261">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>14</v>
+      </c>
+      <c r="C262" t="str">
+        <f>VLOOKUP(B262,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F262">
+        <v>1</v>
+      </c>
+      <c r="G262" t="str">
+        <f>VLOOKUP(F262,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H262">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>8</v>
+      </c>
+      <c r="C263" t="str">
+        <f>VLOOKUP(B263,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F263">
+        <v>12</v>
+      </c>
+      <c r="G263" t="str">
+        <f>VLOOKUP(F263,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H263">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>9</v>
+      </c>
+      <c r="C264" t="str">
+        <f>VLOOKUP(B264,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F264">
+        <v>11</v>
+      </c>
+      <c r="G264" t="str">
+        <f>VLOOKUP(F264,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H264">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>6</v>
+      </c>
+      <c r="C265" t="str">
+        <f>VLOOKUP(B265,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F265">
+        <v>2</v>
+      </c>
+      <c r="G265" t="str">
+        <f>VLOOKUP(F265,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H265">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>13</v>
+      </c>
+      <c r="C266" t="str">
+        <f>VLOOKUP(B266,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F266">
+        <v>10</v>
+      </c>
+      <c r="G266" t="str">
+        <f>VLOOKUP(F266,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H266">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>7</v>
+      </c>
+      <c r="C267" t="str">
+        <f>VLOOKUP(B267,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="F267">
+        <v>3</v>
+      </c>
+      <c r="G267" t="str">
+        <f>VLOOKUP(F267,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="H267">
+        <f t="shared" si="4"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>5</v>
+      </c>
+      <c r="C268" t="str">
+        <f>VLOOKUP(B268,teams!$A$1:$B$15,2)</f>
+        <v>Kaipiras da Gema</v>
+      </c>
+      <c r="F268">
+        <v>1</v>
+      </c>
+      <c r="G268" t="str">
+        <f>VLOOKUP(F268,teams!$A$1:$B$15,2)</f>
+        <v>Alabama Black Bears</v>
+      </c>
+      <c r="H268">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>14</v>
+      </c>
+      <c r="C269" t="str">
+        <f>VLOOKUP(B269,teams!$A$1:$B$15,2)</f>
+        <v>Tchêltics da Peleia</v>
+      </c>
+      <c r="F269">
+        <v>10</v>
+      </c>
+      <c r="G269" t="str">
+        <f>VLOOKUP(F269,teams!$A$1:$B$15,2)</f>
+        <v>Pelotas Vikings</v>
+      </c>
+      <c r="H269">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>8</v>
+      </c>
+      <c r="C270" t="str">
+        <f>VLOOKUP(B270,teams!$A$1:$B$15,2)</f>
+        <v>New Orleans Dancers</v>
+      </c>
+      <c r="F270">
+        <v>2</v>
+      </c>
+      <c r="G270" t="str">
+        <f>VLOOKUP(F270,teams!$A$1:$B$15,2)</f>
+        <v>Franca Celtics</v>
+      </c>
+      <c r="H270">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>9</v>
+      </c>
+      <c r="C271" t="str">
+        <f>VLOOKUP(B271,teams!$A$1:$B$15,2)</f>
+        <v>Osasco Heat</v>
+      </c>
+      <c r="F271">
+        <v>12</v>
+      </c>
+      <c r="G271" t="str">
+        <f>VLOOKUP(F271,teams!$A$1:$B$15,2)</f>
+        <v>Recife Black Diamond</v>
+      </c>
+      <c r="H271">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>3</v>
+      </c>
+      <c r="C272" t="str">
+        <f>VLOOKUP(B272,teams!$A$1:$B$15,2)</f>
+        <v>Guarulhos Nuggets</v>
+      </c>
+      <c r="F272">
+        <v>11</v>
+      </c>
+      <c r="G272" t="str">
+        <f>VLOOKUP(F272,teams!$A$1:$B$15,2)</f>
+        <v>Pernambuco Pharynx</v>
+      </c>
+      <c r="H272">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>13</v>
+      </c>
+      <c r="C273" t="str">
+        <f>VLOOKUP(B273,teams!$A$1:$B$15,2)</f>
+        <v>RJ Black Mamba</v>
+      </c>
+      <c r="F273">
+        <v>7</v>
+      </c>
+      <c r="G273" t="str">
+        <f>VLOOKUP(F273,teams!$A$1:$B$15,2)</f>
+        <v>Montreal Turtles</v>
+      </c>
+      <c r="H273">
+        <f t="shared" si="4"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>6</v>
+      </c>
+      <c r="C274" t="str">
+        <f>VLOOKUP(B274,teams!$A$1:$B$15,2)</f>
+        <v>Miami Barons</v>
+      </c>
+      <c r="F274">
+        <v>4</v>
+      </c>
+      <c r="G274" t="str">
+        <f>VLOOKUP(F274,teams!$A$1:$B$15,2)</f>
+        <v>Itajubá Rabbits</v>
+      </c>
+      <c r="H274">
+        <f t="shared" si="4"/>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
